--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -499,10 +499,10 @@
         <v>9.54</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>51.66</v>
+        <v>51.67</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>42.13</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         <v>61.05</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>54.21</v>
+        <v>54.22</v>
       </c>
     </row>
     <row r="5">
@@ -569,7 +569,7 @@
         <v>-19.91</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>66.55</v>
+        <v>66.54</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>86.46</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_metropolitana_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_metropolitana_provincial.xlsx
@@ -58,7 +58,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>51.67</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>42.12</v>
+        <v>42.13</v>
       </c>
     </row>
     <row r="3">
@@ -569,7 +569,7 @@
         <v>-19.91</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>66.54</v>
+        <v>66.55</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>86.46</v>
